--- a/app/templates_excel/albedo/a8_sys_en.xlsx
+++ b/app/templates_excel/albedo/a8_sys_en.xlsx
@@ -1302,9 +1302,6 @@
     <t>The rainbow's pot of gold.</t>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
   </si>
   <si>
@@ -1500,9 +1497,6 @@
     <t>A clown making grimaces.</t>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-  </si>
-  <si>
     <t>One hand slightly flexed with a very prominent thumb.</t>
   </si>
   <si>
@@ -1596,9 +1590,6 @@
     <t>The human soul awaiting opportunity for expression.</t>
   </si>
   <si>
-    <t>A pagent.</t>
-  </si>
-  <si>
     <t>Sunshine just after a storm.</t>
   </si>
   <si>
@@ -2169,9 +2160,6 @@
     <t>An ancient pottery bowl filled with fresh violets.</t>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-  </si>
-  <si>
     <t>Butterfly emerging from a chrysalis.</t>
   </si>
   <si>
@@ -2229,9 +2217,6 @@
     <t>An Easter promenade.</t>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-  </si>
-  <si>
     <t>A master instructing his pupil.</t>
   </si>
   <si>
@@ -2245,9 +2230,6 @@
   </si>
   <si>
     <t>Spiritist phenomena.</t>
-  </si>
-  <si>
-    <t>An inhibited island.</t>
   </si>
   <si>
     <t>The purging of the priesthood.</t>
@@ -2281,6 +2263,30 @@
   </si>
   <si>
     <t>Rock formations at the edge of a precipice.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4061,7 +4067,7 @@
       <c r="T46" s="1"/>
       <c r="U46" s="1"/>
       <c r="V46" s="20" t="s">
-        <v>423</v>
+        <v>743</v>
       </c>
       <c r="W46" s="1"/>
     </row>
@@ -4090,7 +4096,7 @@
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="20" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="W47" s="1"/>
     </row>
@@ -4119,7 +4125,7 @@
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="20" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="W48" s="1"/>
     </row>
@@ -4148,7 +4154,7 @@
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="20" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4176,7 +4182,7 @@
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4204,7 +4210,7 @@
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="52" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4232,7 +4238,7 @@
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="20" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="53" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4260,7 +4266,7 @@
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="20" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="54" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4288,7 +4294,7 @@
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4316,7 +4322,7 @@
       <c r="T55" s="1"/>
       <c r="U55" s="1"/>
       <c r="V55" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="56" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4344,7 +4350,7 @@
       <c r="T56" s="1"/>
       <c r="U56" s="1"/>
       <c r="V56" s="20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4372,7 +4378,7 @@
       <c r="T57" s="1"/>
       <c r="U57" s="1"/>
       <c r="V57" s="20" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4400,7 +4406,7 @@
       <c r="T58" s="1"/>
       <c r="U58" s="1"/>
       <c r="V58" s="20" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4428,7 +4434,7 @@
       <c r="T59" s="1"/>
       <c r="U59" s="1"/>
       <c r="V59" s="20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="60" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4456,7 +4462,7 @@
       <c r="T60" s="1"/>
       <c r="U60" s="1"/>
       <c r="V60" s="20" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4484,7 +4490,7 @@
       <c r="T61" s="1"/>
       <c r="U61" s="1"/>
       <c r="V61" s="20" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="62" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4512,7 +4518,7 @@
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
       <c r="V62" s="20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="63" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4540,7 +4546,7 @@
       <c r="T63" s="1"/>
       <c r="U63" s="1"/>
       <c r="V63" s="20" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="64" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -4568,7 +4574,7 @@
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="20" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
@@ -4596,7 +4602,7 @@
       <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="20" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="W65" s="1"/>
     </row>
@@ -4625,7 +4631,7 @@
       <c r="T66" s="1"/>
       <c r="U66" s="1"/>
       <c r="V66" s="20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="W66" s="1"/>
     </row>
@@ -4654,7 +4660,7 @@
       <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="20" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="W67" s="1"/>
     </row>
@@ -4683,7 +4689,7 @@
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
       <c r="V68" s="20" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="W68" s="1"/>
     </row>
@@ -4712,7 +4718,7 @@
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="20" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="W69" s="1"/>
     </row>
@@ -4741,7 +4747,7 @@
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="20" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="W70" s="1"/>
     </row>
@@ -4770,7 +4776,7 @@
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="20" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="W71" s="1"/>
     </row>
@@ -4868,7 +4874,7 @@
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="20" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="W73" s="1"/>
     </row>
@@ -4897,7 +4903,7 @@
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
       <c r="V74" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="W74" s="1"/>
     </row>
@@ -4926,7 +4932,7 @@
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
       <c r="V75" s="20" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="W75" s="1"/>
     </row>
@@ -4955,7 +4961,7 @@
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
       <c r="V76" s="20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="W76" s="1"/>
     </row>
@@ -4984,7 +4990,7 @@
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
       <c r="V77" s="20" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="W77" s="1"/>
     </row>
@@ -5013,7 +5019,7 @@
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
       <c r="V78" s="20" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="W78" s="1"/>
     </row>
@@ -5042,7 +5048,7 @@
       <c r="T79" s="1"/>
       <c r="U79" s="1"/>
       <c r="V79" s="20" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="W79" s="1"/>
     </row>
@@ -5071,7 +5077,7 @@
       <c r="T80" s="1"/>
       <c r="U80" s="1"/>
       <c r="V80" s="20" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="W80" s="1"/>
     </row>
@@ -5100,7 +5106,7 @@
       <c r="T81" s="1"/>
       <c r="U81" s="1"/>
       <c r="V81" s="20" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="82" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5128,7 +5134,7 @@
       <c r="T82" s="1"/>
       <c r="U82" s="1"/>
       <c r="V82" s="20" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="83" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5156,7 +5162,7 @@
       <c r="T83" s="1"/>
       <c r="U83" s="1"/>
       <c r="V83" s="20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="84" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5184,7 +5190,7 @@
       <c r="T84" s="1"/>
       <c r="U84" s="1"/>
       <c r="V84" s="20" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="85" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5212,7 +5218,7 @@
       <c r="T85" s="1"/>
       <c r="U85" s="1"/>
       <c r="V85" s="20" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="86" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5240,7 +5246,7 @@
       <c r="T86" s="1"/>
       <c r="U86" s="1"/>
       <c r="V86" s="20" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="87" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5268,7 +5274,7 @@
       <c r="T87" s="1"/>
       <c r="U87" s="1"/>
       <c r="V87" s="20" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="88" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5296,7 +5302,7 @@
       <c r="T88" s="1"/>
       <c r="U88" s="1"/>
       <c r="V88" s="20" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="89" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5324,7 +5330,7 @@
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
       <c r="V89" s="20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5352,7 +5358,7 @@
       <c r="T90" s="1"/>
       <c r="U90" s="1"/>
       <c r="V90" s="20" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="91" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5380,7 +5386,7 @@
       <c r="T91" s="1"/>
       <c r="U91" s="1"/>
       <c r="V91" s="20" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="92" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5408,7 +5414,7 @@
       <c r="T92" s="1"/>
       <c r="U92" s="1"/>
       <c r="V92" s="20" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="93" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5436,7 +5442,7 @@
       <c r="T93" s="1"/>
       <c r="U93" s="1"/>
       <c r="V93" s="20" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="94" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5464,7 +5470,7 @@
       <c r="T94" s="1"/>
       <c r="U94" s="1"/>
       <c r="V94" s="20" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="95" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5492,7 +5498,7 @@
       <c r="T95" s="1"/>
       <c r="U95" s="1"/>
       <c r="V95" s="20" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="96" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -5520,7 +5526,7 @@
       <c r="T96" s="1"/>
       <c r="U96" s="1"/>
       <c r="V96" s="20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="97" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
@@ -5548,7 +5554,7 @@
       <c r="T97" s="1"/>
       <c r="U97" s="1"/>
       <c r="V97" s="20" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="W97" s="1"/>
     </row>
@@ -5577,7 +5583,7 @@
       <c r="T98" s="1"/>
       <c r="U98" s="1"/>
       <c r="V98" s="20" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="W98" s="1"/>
     </row>
@@ -5606,7 +5612,7 @@
       <c r="T99" s="1"/>
       <c r="U99" s="1"/>
       <c r="V99" s="20" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="W99" s="1"/>
     </row>
@@ -5635,7 +5641,7 @@
       <c r="T100" s="1"/>
       <c r="U100" s="1"/>
       <c r="V100" s="20" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="W100" s="1"/>
     </row>
@@ -5664,7 +5670,7 @@
       <c r="T101" s="1"/>
       <c r="U101" s="1"/>
       <c r="V101" s="20" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="W101" s="1"/>
     </row>
@@ -5693,7 +5699,7 @@
       <c r="T102" s="1"/>
       <c r="U102" s="1"/>
       <c r="V102" s="20" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="W102" s="1"/>
     </row>
@@ -5791,7 +5797,7 @@
       <c r="T104" s="1"/>
       <c r="U104" s="1"/>
       <c r="V104" s="20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="W104" s="1"/>
     </row>
@@ -5820,7 +5826,7 @@
       <c r="T105" s="1"/>
       <c r="U105" s="1"/>
       <c r="V105" s="20" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="W105" s="1"/>
     </row>
@@ -5849,7 +5855,7 @@
       <c r="T106" s="1"/>
       <c r="U106" s="1"/>
       <c r="V106" s="20" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="W106" s="1"/>
     </row>
@@ -5878,7 +5884,7 @@
       <c r="T107" s="1"/>
       <c r="U107" s="1"/>
       <c r="V107" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="W107" s="1"/>
     </row>
@@ -5907,7 +5913,7 @@
       <c r="T108" s="1"/>
       <c r="U108" s="1"/>
       <c r="V108" s="20" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="W108" s="1"/>
     </row>
@@ -5936,7 +5942,7 @@
       <c r="T109" s="1"/>
       <c r="U109" s="1"/>
       <c r="V109" s="20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="W109" s="1"/>
     </row>
@@ -5965,7 +5971,7 @@
       <c r="T110" s="1"/>
       <c r="U110" s="1"/>
       <c r="V110" s="20" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="W110" s="1"/>
     </row>
@@ -5994,7 +6000,7 @@
       <c r="T111" s="1"/>
       <c r="U111" s="1"/>
       <c r="V111" s="20" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="W111" s="1"/>
     </row>
@@ -6023,7 +6029,7 @@
       <c r="T112" s="1"/>
       <c r="U112" s="1"/>
       <c r="V112" s="20" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="W112" s="1"/>
     </row>
@@ -6052,7 +6058,7 @@
       <c r="T113" s="1"/>
       <c r="U113" s="1"/>
       <c r="V113" s="20" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="114" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6080,7 +6086,7 @@
       <c r="T114" s="1"/>
       <c r="U114" s="1"/>
       <c r="V114" s="20" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="115" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6108,7 +6114,7 @@
       <c r="T115" s="1"/>
       <c r="U115" s="1"/>
       <c r="V115" s="20" t="s">
-        <v>489</v>
+        <v>744</v>
       </c>
     </row>
     <row r="116" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6136,7 +6142,7 @@
       <c r="T116" s="1"/>
       <c r="U116" s="1"/>
       <c r="V116" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="117" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6164,7 +6170,7 @@
       <c r="T117" s="1"/>
       <c r="U117" s="1"/>
       <c r="V117" s="20" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="118" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6192,7 +6198,7 @@
       <c r="T118" s="1"/>
       <c r="U118" s="1"/>
       <c r="V118" s="20" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="119" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6220,7 +6226,7 @@
       <c r="T119" s="1"/>
       <c r="U119" s="1"/>
       <c r="V119" s="20" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="120" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6248,7 +6254,7 @@
       <c r="T120" s="1"/>
       <c r="U120" s="1"/>
       <c r="V120" s="20" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="121" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6276,7 +6282,7 @@
       <c r="T121" s="1"/>
       <c r="U121" s="1"/>
       <c r="V121" s="20" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="122" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6304,7 +6310,7 @@
       <c r="T122" s="1"/>
       <c r="U122" s="1"/>
       <c r="V122" s="20" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="123" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6332,7 +6338,7 @@
       <c r="T123" s="1"/>
       <c r="U123" s="1"/>
       <c r="V123" s="20" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="124" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6360,7 +6366,7 @@
       <c r="T124" s="1"/>
       <c r="U124" s="1"/>
       <c r="V124" s="20" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="125" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6388,7 +6394,7 @@
       <c r="T125" s="1"/>
       <c r="U125" s="1"/>
       <c r="V125" s="20" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="126" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6416,7 +6422,7 @@
       <c r="T126" s="1"/>
       <c r="U126" s="1"/>
       <c r="V126" s="20" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="127" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6444,7 +6450,7 @@
       <c r="T127" s="1"/>
       <c r="U127" s="1"/>
       <c r="V127" s="20" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="128" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
@@ -6472,7 +6478,7 @@
       <c r="T128" s="1"/>
       <c r="U128" s="1"/>
       <c r="V128" s="20" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="129" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
@@ -6500,7 +6506,7 @@
       <c r="T129" s="1"/>
       <c r="U129" s="1"/>
       <c r="V129" s="20" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="W129" s="1"/>
     </row>
@@ -6529,7 +6535,7 @@
       <c r="T130" s="1"/>
       <c r="U130" s="1"/>
       <c r="V130" s="20" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="W130" s="1"/>
     </row>
@@ -6558,11 +6564,11 @@
       <c r="T131" s="1"/>
       <c r="U131" s="1"/>
       <c r="V131" s="20" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="W131" s="1"/>
     </row>
-    <row r="132" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A132" s="12" t="s">
         <v>130</v>
       </c>
@@ -6587,11 +6593,11 @@
       <c r="T132" s="1"/>
       <c r="U132" s="1"/>
       <c r="V132" s="20" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="W132" s="1"/>
     </row>
-    <row r="133" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A133" s="12" t="s">
         <v>131</v>
       </c>
@@ -6616,11 +6622,11 @@
       <c r="T133" s="1"/>
       <c r="U133" s="1"/>
       <c r="V133" s="20" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="W133" s="1"/>
     </row>
-    <row r="134" spans="1:23" s="15" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:23" s="15" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="16"/>
       <c r="B134" s="16" t="s">
         <v>41</v>
@@ -6689,7 +6695,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="135" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A135" s="8" t="s">
         <v>132</v>
       </c>
@@ -6714,11 +6720,11 @@
       <c r="T135" s="1"/>
       <c r="U135" s="1"/>
       <c r="V135" s="20" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="W135" s="1"/>
     </row>
-    <row r="136" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A136" s="8" t="s">
         <v>133</v>
       </c>
@@ -6743,11 +6749,11 @@
       <c r="T136" s="1"/>
       <c r="U136" s="1"/>
       <c r="V136" s="20" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="W136" s="1"/>
     </row>
-    <row r="137" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A137" s="8" t="s">
         <v>134</v>
       </c>
@@ -6772,11 +6778,11 @@
       <c r="T137" s="1"/>
       <c r="U137" s="1"/>
       <c r="V137" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W137" s="1"/>
     </row>
-    <row r="138" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A138" s="8" t="s">
         <v>135</v>
       </c>
@@ -6801,11 +6807,11 @@
       <c r="T138" s="1"/>
       <c r="U138" s="1"/>
       <c r="V138" s="20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="W138" s="1"/>
     </row>
-    <row r="139" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A139" s="8" t="s">
         <v>136</v>
       </c>
@@ -6830,11 +6836,11 @@
       <c r="T139" s="1"/>
       <c r="U139" s="1"/>
       <c r="V139" s="20" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="W139" s="1"/>
     </row>
-    <row r="140" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A140" s="8" t="s">
         <v>137</v>
       </c>
@@ -6859,11 +6865,11 @@
       <c r="T140" s="1"/>
       <c r="U140" s="1"/>
       <c r="V140" s="20" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="W140" s="1"/>
     </row>
-    <row r="141" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A141" s="8" t="s">
         <v>138</v>
       </c>
@@ -6888,11 +6894,11 @@
       <c r="T141" s="1"/>
       <c r="U141" s="1"/>
       <c r="V141" s="20" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="W141" s="1"/>
     </row>
-    <row r="142" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A142" s="8" t="s">
         <v>139</v>
       </c>
@@ -6917,11 +6923,11 @@
       <c r="T142" s="1"/>
       <c r="U142" s="1"/>
       <c r="V142" s="20" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W142" s="1"/>
     </row>
-    <row r="143" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A143" s="8" t="s">
         <v>140</v>
       </c>
@@ -6946,11 +6952,11 @@
       <c r="T143" s="1"/>
       <c r="U143" s="1"/>
       <c r="V143" s="20" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="W143" s="1"/>
     </row>
-    <row r="144" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A144" s="8" t="s">
         <v>141</v>
       </c>
@@ -6975,11 +6981,11 @@
       <c r="T144" s="1"/>
       <c r="U144" s="1"/>
       <c r="V144" s="20" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="W144" s="1"/>
     </row>
-    <row r="145" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A145" s="8" t="s">
         <v>142</v>
       </c>
@@ -7004,10 +7010,10 @@
       <c r="T145" s="1"/>
       <c r="U145" s="1"/>
       <c r="V145" s="20" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="146" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="146" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A146" s="8" t="s">
         <v>143</v>
       </c>
@@ -7032,10 +7038,10 @@
       <c r="T146" s="1"/>
       <c r="U146" s="1"/>
       <c r="V146" s="20" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="147" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="147" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A147" s="8" t="s">
         <v>144</v>
       </c>
@@ -7060,10 +7066,10 @@
       <c r="T147" s="1"/>
       <c r="U147" s="1"/>
       <c r="V147" s="20" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="148" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="148" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A148" s="8" t="s">
         <v>145</v>
       </c>
@@ -7088,10 +7094,10 @@
       <c r="T148" s="1"/>
       <c r="U148" s="1"/>
       <c r="V148" s="20" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="149" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="149" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A149" s="8" t="s">
         <v>146</v>
       </c>
@@ -7116,10 +7122,10 @@
       <c r="T149" s="1"/>
       <c r="U149" s="1"/>
       <c r="V149" s="20" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="150" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="150" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A150" s="8" t="s">
         <v>147</v>
       </c>
@@ -7144,10 +7150,10 @@
       <c r="T150" s="1"/>
       <c r="U150" s="1"/>
       <c r="V150" s="20" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="151" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="151" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A151" s="8" t="s">
         <v>148</v>
       </c>
@@ -7172,10 +7178,10 @@
       <c r="T151" s="1"/>
       <c r="U151" s="1"/>
       <c r="V151" s="20" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="152" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="152" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A152" s="8" t="s">
         <v>149</v>
       </c>
@@ -7200,10 +7206,10 @@
       <c r="T152" s="1"/>
       <c r="U152" s="1"/>
       <c r="V152" s="20" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="153" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="153" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A153" s="8" t="s">
         <v>150</v>
       </c>
@@ -7228,10 +7234,10 @@
       <c r="T153" s="1"/>
       <c r="U153" s="1"/>
       <c r="V153" s="20" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="154" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="154" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A154" s="8" t="s">
         <v>151</v>
       </c>
@@ -7256,10 +7262,10 @@
       <c r="T154" s="1"/>
       <c r="U154" s="1"/>
       <c r="V154" s="20" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="155" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="155" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A155" s="8" t="s">
         <v>152</v>
       </c>
@@ -7284,10 +7290,10 @@
       <c r="T155" s="1"/>
       <c r="U155" s="1"/>
       <c r="V155" s="20" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="156" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="156" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A156" s="8" t="s">
         <v>153</v>
       </c>
@@ -7312,10 +7318,10 @@
       <c r="T156" s="1"/>
       <c r="U156" s="1"/>
       <c r="V156" s="20" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="157" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="157" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A157" s="8" t="s">
         <v>154</v>
       </c>
@@ -7340,10 +7346,10 @@
       <c r="T157" s="1"/>
       <c r="U157" s="1"/>
       <c r="V157" s="20" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="158" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="158" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A158" s="8" t="s">
         <v>155</v>
       </c>
@@ -7368,10 +7374,10 @@
       <c r="T158" s="1"/>
       <c r="U158" s="1"/>
       <c r="V158" s="20" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="159" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="159" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A159" s="8" t="s">
         <v>156</v>
       </c>
@@ -7396,10 +7402,10 @@
       <c r="T159" s="1"/>
       <c r="U159" s="1"/>
       <c r="V159" s="20" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="160" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="160" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A160" s="8" t="s">
         <v>157</v>
       </c>
@@ -7424,10 +7430,10 @@
       <c r="T160" s="1"/>
       <c r="U160" s="1"/>
       <c r="V160" s="20" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="161" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A161" s="8" t="s">
         <v>158</v>
       </c>
@@ -7452,11 +7458,11 @@
       <c r="T161" s="1"/>
       <c r="U161" s="1"/>
       <c r="V161" s="20" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="W161" s="1"/>
     </row>
-    <row r="162" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A162" s="8" t="s">
         <v>159</v>
       </c>
@@ -7481,11 +7487,11 @@
       <c r="T162" s="1"/>
       <c r="U162" s="1"/>
       <c r="V162" s="20" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="W162" s="1"/>
     </row>
-    <row r="163" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A163" s="8" t="s">
         <v>160</v>
       </c>
@@ -7510,11 +7516,11 @@
       <c r="T163" s="1"/>
       <c r="U163" s="1"/>
       <c r="V163" s="20" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="W163" s="1"/>
     </row>
-    <row r="164" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A164" s="8" t="s">
         <v>161</v>
       </c>
@@ -7539,11 +7545,11 @@
       <c r="T164" s="1"/>
       <c r="U164" s="1"/>
       <c r="V164" s="20" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="W164" s="1"/>
     </row>
-    <row r="165" spans="1:23" s="15" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:23" s="15" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="16"/>
       <c r="B165" s="16" t="s">
         <v>41</v>
@@ -7612,7 +7618,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="166" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A166" s="10" t="s">
         <v>162</v>
       </c>
@@ -7637,11 +7643,11 @@
       <c r="T166" s="1"/>
       <c r="U166" s="1"/>
       <c r="V166" s="20" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="W166" s="1"/>
     </row>
-    <row r="167" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A167" s="10" t="s">
         <v>163</v>
       </c>
@@ -7666,11 +7672,11 @@
       <c r="T167" s="1"/>
       <c r="U167" s="1"/>
       <c r="V167" s="20" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="W167" s="1"/>
     </row>
-    <row r="168" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A168" s="10" t="s">
         <v>164</v>
       </c>
@@ -7695,11 +7701,11 @@
       <c r="T168" s="1"/>
       <c r="U168" s="1"/>
       <c r="V168" s="20" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="W168" s="1"/>
     </row>
-    <row r="169" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A169" s="10" t="s">
         <v>165</v>
       </c>
@@ -7724,11 +7730,11 @@
       <c r="T169" s="1"/>
       <c r="U169" s="1"/>
       <c r="V169" s="20" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="W169" s="1"/>
     </row>
-    <row r="170" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A170" s="10" t="s">
         <v>166</v>
       </c>
@@ -7753,11 +7759,11 @@
       <c r="T170" s="1"/>
       <c r="U170" s="1"/>
       <c r="V170" s="20" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="W170" s="1"/>
     </row>
-    <row r="171" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A171" s="10" t="s">
         <v>167</v>
       </c>
@@ -7782,11 +7788,11 @@
       <c r="T171" s="1"/>
       <c r="U171" s="1"/>
       <c r="V171" s="20" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="W171" s="1"/>
     </row>
-    <row r="172" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A172" s="10" t="s">
         <v>168</v>
       </c>
@@ -7811,11 +7817,11 @@
       <c r="T172" s="1"/>
       <c r="U172" s="1"/>
       <c r="V172" s="20" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="W172" s="1"/>
     </row>
-    <row r="173" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A173" s="10" t="s">
         <v>169</v>
       </c>
@@ -7840,11 +7846,11 @@
       <c r="T173" s="1"/>
       <c r="U173" s="1"/>
       <c r="V173" s="20" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="W173" s="1"/>
     </row>
-    <row r="174" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A174" s="10" t="s">
         <v>170</v>
       </c>
@@ -7869,11 +7875,11 @@
       <c r="T174" s="1"/>
       <c r="U174" s="1"/>
       <c r="V174" s="20" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="W174" s="1"/>
     </row>
-    <row r="175" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A175" s="10" t="s">
         <v>171</v>
       </c>
@@ -7898,11 +7904,11 @@
       <c r="T175" s="1"/>
       <c r="U175" s="1"/>
       <c r="V175" s="20" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="W175" s="1"/>
     </row>
-    <row r="176" spans="1:23" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A176" s="10" t="s">
         <v>172</v>
       </c>
@@ -7927,11 +7933,11 @@
       <c r="T176" s="1"/>
       <c r="U176" s="1"/>
       <c r="V176" s="20" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="W176" s="1"/>
     </row>
-    <row r="177" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A177" s="10" t="s">
         <v>173</v>
       </c>
@@ -7956,10 +7962,10 @@
       <c r="T177" s="1"/>
       <c r="U177" s="1"/>
       <c r="V177" s="20" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="178" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="178" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A178" s="10" t="s">
         <v>174</v>
       </c>
@@ -7984,10 +7990,10 @@
       <c r="T178" s="1"/>
       <c r="U178" s="1"/>
       <c r="V178" s="20" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="179" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="179" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A179" s="10" t="s">
         <v>175</v>
       </c>
@@ -8012,10 +8018,10 @@
       <c r="T179" s="1"/>
       <c r="U179" s="1"/>
       <c r="V179" s="20" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="180" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="180" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A180" s="10" t="s">
         <v>176</v>
       </c>
@@ -8040,10 +8046,10 @@
       <c r="T180" s="1"/>
       <c r="U180" s="1"/>
       <c r="V180" s="20" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="181" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="181" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A181" s="10" t="s">
         <v>177</v>
       </c>
@@ -8068,10 +8074,10 @@
       <c r="T181" s="1"/>
       <c r="U181" s="1"/>
       <c r="V181" s="20" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="182" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="182" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A182" s="10" t="s">
         <v>178</v>
       </c>
@@ -8096,10 +8102,10 @@
       <c r="T182" s="1"/>
       <c r="U182" s="1"/>
       <c r="V182" s="20" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="183" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="183" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A183" s="10" t="s">
         <v>179</v>
       </c>
@@ -8124,10 +8130,10 @@
       <c r="T183" s="1"/>
       <c r="U183" s="1"/>
       <c r="V183" s="20" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="184" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="184" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A184" s="10" t="s">
         <v>180</v>
       </c>
@@ -8152,10 +8158,10 @@
       <c r="T184" s="1"/>
       <c r="U184" s="1"/>
       <c r="V184" s="20" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="185" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="185" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A185" s="10" t="s">
         <v>181</v>
       </c>
@@ -8180,10 +8186,10 @@
       <c r="T185" s="1"/>
       <c r="U185" s="1"/>
       <c r="V185" s="20" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="186" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="186" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A186" s="10" t="s">
         <v>182</v>
       </c>
@@ -8208,10 +8214,10 @@
       <c r="T186" s="1"/>
       <c r="U186" s="1"/>
       <c r="V186" s="20" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="187" spans="1:22" ht="16.5" x14ac:dyDescent="0.3">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="187" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A187" s="10" t="s">
         <v>183</v>
       </c>
@@ -8236,7 +8242,7 @@
       <c r="T187" s="1"/>
       <c r="U187" s="1"/>
       <c r="V187" s="20" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="188" spans="1:22" x14ac:dyDescent="0.4">
@@ -8264,7 +8270,7 @@
       <c r="T188" s="1"/>
       <c r="U188" s="1"/>
       <c r="V188" s="20" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.4">
@@ -8292,7 +8298,7 @@
       <c r="T189" s="1"/>
       <c r="U189" s="1"/>
       <c r="V189" s="20" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.4">
@@ -8320,7 +8326,7 @@
       <c r="T190" s="1"/>
       <c r="U190" s="1"/>
       <c r="V190" s="20" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="191" spans="1:22" x14ac:dyDescent="0.4">
@@ -8348,7 +8354,7 @@
       <c r="T191" s="1"/>
       <c r="U191" s="1"/>
       <c r="V191" s="20" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="192" spans="1:22" x14ac:dyDescent="0.4">
@@ -8376,7 +8382,7 @@
       <c r="T192" s="1"/>
       <c r="U192" s="1"/>
       <c r="V192" s="20" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.4">
@@ -8404,7 +8410,7 @@
       <c r="T193" s="1"/>
       <c r="U193" s="1"/>
       <c r="V193" s="20" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="W193" s="1"/>
     </row>
@@ -8433,7 +8439,7 @@
       <c r="T194" s="1"/>
       <c r="U194" s="1"/>
       <c r="V194" s="20" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="W194" s="1"/>
     </row>
@@ -8462,7 +8468,7 @@
       <c r="T195" s="1"/>
       <c r="U195" s="1"/>
       <c r="V195" s="20" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="W195" s="1"/>
     </row>
@@ -8560,7 +8566,7 @@
       <c r="T197" s="1"/>
       <c r="U197" s="1"/>
       <c r="V197" s="20" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="W197" s="1"/>
     </row>
@@ -8589,7 +8595,7 @@
       <c r="T198" s="1"/>
       <c r="U198" s="1"/>
       <c r="V198" s="20" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="W198" s="1"/>
     </row>
@@ -8618,7 +8624,7 @@
       <c r="T199" s="1"/>
       <c r="U199" s="1"/>
       <c r="V199" s="20" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="W199" s="1"/>
     </row>
@@ -8647,7 +8653,7 @@
       <c r="T200" s="1"/>
       <c r="U200" s="1"/>
       <c r="V200" s="20" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="W200" s="1"/>
     </row>
@@ -8676,7 +8682,7 @@
       <c r="T201" s="1"/>
       <c r="U201" s="1"/>
       <c r="V201" s="20" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="W201" s="1"/>
     </row>
@@ -8705,7 +8711,7 @@
       <c r="T202" s="1"/>
       <c r="U202" s="1"/>
       <c r="V202" s="20" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="W202" s="1"/>
     </row>
@@ -8734,7 +8740,7 @@
       <c r="T203" s="1"/>
       <c r="U203" s="1"/>
       <c r="V203" s="20" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="W203" s="1"/>
     </row>
@@ -8763,7 +8769,7 @@
       <c r="T204" s="1"/>
       <c r="U204" s="1"/>
       <c r="V204" s="20" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="W204" s="1"/>
     </row>
@@ -8792,7 +8798,7 @@
       <c r="T205" s="1"/>
       <c r="U205" s="1"/>
       <c r="V205" s="20" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="W205" s="1"/>
     </row>
@@ -8821,7 +8827,7 @@
       <c r="T206" s="1"/>
       <c r="U206" s="1"/>
       <c r="V206" s="20" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="W206" s="1"/>
     </row>
@@ -8850,7 +8856,7 @@
       <c r="T207" s="1"/>
       <c r="U207" s="1"/>
       <c r="V207" s="20" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="W207" s="1"/>
     </row>
@@ -8879,7 +8885,7 @@
       <c r="T208" s="1"/>
       <c r="U208" s="1"/>
       <c r="V208" s="20" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="W208" s="1"/>
     </row>
@@ -8908,7 +8914,7 @@
       <c r="T209" s="1"/>
       <c r="U209" s="1"/>
       <c r="V209" s="20" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="210" spans="1:22" x14ac:dyDescent="0.4">
@@ -8936,7 +8942,7 @@
       <c r="T210" s="1"/>
       <c r="U210" s="1"/>
       <c r="V210" s="20" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="211" spans="1:22" x14ac:dyDescent="0.4">
@@ -8964,7 +8970,7 @@
       <c r="T211" s="1"/>
       <c r="U211" s="1"/>
       <c r="V211" s="20" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="212" spans="1:22" x14ac:dyDescent="0.4">
@@ -8992,7 +8998,7 @@
       <c r="T212" s="1"/>
       <c r="U212" s="1"/>
       <c r="V212" s="20" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="213" spans="1:22" x14ac:dyDescent="0.4">
@@ -9020,7 +9026,7 @@
       <c r="T213" s="1"/>
       <c r="U213" s="1"/>
       <c r="V213" s="20" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="214" spans="1:22" x14ac:dyDescent="0.4">
@@ -9048,7 +9054,7 @@
       <c r="T214" s="1"/>
       <c r="U214" s="1"/>
       <c r="V214" s="20" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="215" spans="1:22" x14ac:dyDescent="0.4">
@@ -9076,7 +9082,7 @@
       <c r="T215" s="1"/>
       <c r="U215" s="1"/>
       <c r="V215" s="20" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="216" spans="1:22" x14ac:dyDescent="0.4">
@@ -9104,7 +9110,7 @@
       <c r="T216" s="1"/>
       <c r="U216" s="1"/>
       <c r="V216" s="20" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.4">
@@ -9132,7 +9138,7 @@
       <c r="T217" s="1"/>
       <c r="U217" s="1"/>
       <c r="V217" s="20" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="218" spans="1:22" x14ac:dyDescent="0.4">
@@ -9160,7 +9166,7 @@
       <c r="T218" s="1"/>
       <c r="U218" s="1"/>
       <c r="V218" s="20" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="219" spans="1:22" x14ac:dyDescent="0.4">
@@ -9188,7 +9194,7 @@
       <c r="T219" s="1"/>
       <c r="U219" s="1"/>
       <c r="V219" s="20" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="220" spans="1:22" x14ac:dyDescent="0.4">
@@ -9216,7 +9222,7 @@
       <c r="T220" s="1"/>
       <c r="U220" s="1"/>
       <c r="V220" s="20" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="221" spans="1:22" x14ac:dyDescent="0.4">
@@ -9244,7 +9250,7 @@
       <c r="T221" s="1"/>
       <c r="U221" s="1"/>
       <c r="V221" s="20" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="222" spans="1:22" x14ac:dyDescent="0.4">
@@ -9272,7 +9278,7 @@
       <c r="T222" s="1"/>
       <c r="U222" s="1"/>
       <c r="V222" s="20" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.4">
@@ -9300,7 +9306,7 @@
       <c r="T223" s="1"/>
       <c r="U223" s="1"/>
       <c r="V223" s="20" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="224" spans="1:22" x14ac:dyDescent="0.4">
@@ -9328,7 +9334,7 @@
       <c r="T224" s="1"/>
       <c r="U224" s="1"/>
       <c r="V224" s="20" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.4">
@@ -9356,7 +9362,7 @@
       <c r="T225" s="1"/>
       <c r="U225" s="1"/>
       <c r="V225" s="20" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="W225" s="1"/>
     </row>
@@ -9385,7 +9391,7 @@
       <c r="T226" s="1"/>
       <c r="U226" s="1"/>
       <c r="V226" s="20" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="W226" s="1"/>
     </row>
@@ -9483,7 +9489,7 @@
       <c r="T228" s="1"/>
       <c r="U228" s="1"/>
       <c r="V228" s="20" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="W228" s="1"/>
     </row>
@@ -9512,7 +9518,7 @@
       <c r="T229" s="1"/>
       <c r="U229" s="1"/>
       <c r="V229" s="20" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="W229" s="1"/>
     </row>
@@ -9541,7 +9547,7 @@
       <c r="T230" s="1"/>
       <c r="U230" s="1"/>
       <c r="V230" s="20" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="W230" s="1"/>
     </row>
@@ -9570,7 +9576,7 @@
       <c r="T231" s="1"/>
       <c r="U231" s="1"/>
       <c r="V231" s="20" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="W231" s="1"/>
     </row>
@@ -9599,7 +9605,7 @@
       <c r="T232" s="1"/>
       <c r="U232" s="1"/>
       <c r="V232" s="20" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="W232" s="1"/>
     </row>
@@ -9628,7 +9634,7 @@
       <c r="T233" s="1"/>
       <c r="U233" s="1"/>
       <c r="V233" s="20" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="W233" s="1"/>
     </row>
@@ -9657,7 +9663,7 @@
       <c r="T234" s="1"/>
       <c r="U234" s="1"/>
       <c r="V234" s="20" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="W234" s="1"/>
     </row>
@@ -9686,7 +9692,7 @@
       <c r="T235" s="1"/>
       <c r="U235" s="1"/>
       <c r="V235" s="20" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="W235" s="1"/>
     </row>
@@ -9715,7 +9721,7 @@
       <c r="T236" s="1"/>
       <c r="U236" s="1"/>
       <c r="V236" s="20" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="W236" s="1"/>
     </row>
@@ -9744,7 +9750,7 @@
       <c r="T237" s="1"/>
       <c r="U237" s="1"/>
       <c r="V237" s="20" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="W237" s="1"/>
     </row>
@@ -9773,7 +9779,7 @@
       <c r="T238" s="1"/>
       <c r="U238" s="1"/>
       <c r="V238" s="20" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="W238" s="1"/>
     </row>
@@ -9802,7 +9808,7 @@
       <c r="T239" s="1"/>
       <c r="U239" s="1"/>
       <c r="V239" s="20" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="W239" s="1"/>
     </row>
@@ -9831,7 +9837,7 @@
       <c r="T240" s="1"/>
       <c r="U240" s="1"/>
       <c r="V240" s="20" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="W240" s="1"/>
     </row>
@@ -9860,7 +9866,7 @@
       <c r="T241" s="1"/>
       <c r="U241" s="1"/>
       <c r="V241" s="20" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.4">
@@ -9888,7 +9894,7 @@
       <c r="T242" s="1"/>
       <c r="U242" s="1"/>
       <c r="V242" s="20" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.4">
@@ -9916,7 +9922,7 @@
       <c r="T243" s="1"/>
       <c r="U243" s="1"/>
       <c r="V243" s="20" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.4">
@@ -9944,7 +9950,7 @@
       <c r="T244" s="1"/>
       <c r="U244" s="1"/>
       <c r="V244" s="20" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.4">
@@ -9972,7 +9978,7 @@
       <c r="T245" s="1"/>
       <c r="U245" s="1"/>
       <c r="V245" s="20" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.4">
@@ -10000,7 +10006,7 @@
       <c r="T246" s="1"/>
       <c r="U246" s="1"/>
       <c r="V246" s="20" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.4">
@@ -10028,7 +10034,7 @@
       <c r="T247" s="1"/>
       <c r="U247" s="1"/>
       <c r="V247" s="20" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.4">
@@ -10056,7 +10062,7 @@
       <c r="T248" s="1"/>
       <c r="U248" s="1"/>
       <c r="V248" s="20" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.4">
@@ -10084,7 +10090,7 @@
       <c r="T249" s="1"/>
       <c r="U249" s="1"/>
       <c r="V249" s="20" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.4">
@@ -10112,7 +10118,7 @@
       <c r="T250" s="1"/>
       <c r="U250" s="1"/>
       <c r="V250" s="20" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.4">
@@ -10140,7 +10146,7 @@
       <c r="T251" s="1"/>
       <c r="U251" s="1"/>
       <c r="V251" s="20" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.4">
@@ -10168,7 +10174,7 @@
       <c r="T252" s="1"/>
       <c r="U252" s="1"/>
       <c r="V252" s="20" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="253" spans="1:22" x14ac:dyDescent="0.4">
@@ -10196,7 +10202,7 @@
       <c r="T253" s="1"/>
       <c r="U253" s="1"/>
       <c r="V253" s="20" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="254" spans="1:22" x14ac:dyDescent="0.4">
@@ -10224,7 +10230,7 @@
       <c r="T254" s="1"/>
       <c r="U254" s="1"/>
       <c r="V254" s="20" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="255" spans="1:22" x14ac:dyDescent="0.4">
@@ -10252,7 +10258,7 @@
       <c r="T255" s="1"/>
       <c r="U255" s="1"/>
       <c r="V255" s="20" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="256" spans="1:22" x14ac:dyDescent="0.4">
@@ -10280,7 +10286,7 @@
       <c r="T256" s="1"/>
       <c r="U256" s="1"/>
       <c r="V256" s="20" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.4">
@@ -10308,7 +10314,7 @@
       <c r="T257" s="1"/>
       <c r="U257" s="1"/>
       <c r="V257" s="20" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="W257" s="1"/>
     </row>
@@ -10406,7 +10412,7 @@
       <c r="T259" s="1"/>
       <c r="U259" s="1"/>
       <c r="V259" s="20" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="W259" s="1"/>
     </row>
@@ -10435,7 +10441,7 @@
       <c r="T260" s="1"/>
       <c r="U260" s="1"/>
       <c r="V260" s="20" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="W260" s="1"/>
     </row>
@@ -10464,7 +10470,7 @@
       <c r="T261" s="1"/>
       <c r="U261" s="1"/>
       <c r="V261" s="20" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="W261" s="1"/>
     </row>
@@ -10493,7 +10499,7 @@
       <c r="T262" s="1"/>
       <c r="U262" s="1"/>
       <c r="V262" s="20" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="W262" s="1"/>
     </row>
@@ -10522,7 +10528,7 @@
       <c r="T263" s="1"/>
       <c r="U263" s="1"/>
       <c r="V263" s="20" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="W263" s="1"/>
     </row>
@@ -10551,7 +10557,7 @@
       <c r="T264" s="1"/>
       <c r="U264" s="1"/>
       <c r="V264" s="20" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="W264" s="1"/>
     </row>
@@ -10580,7 +10586,7 @@
       <c r="T265" s="1"/>
       <c r="U265" s="1"/>
       <c r="V265" s="20" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="W265" s="1"/>
     </row>
@@ -10609,7 +10615,7 @@
       <c r="T266" s="1"/>
       <c r="U266" s="1"/>
       <c r="V266" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="W266" s="1"/>
     </row>
@@ -10638,7 +10644,7 @@
       <c r="T267" s="1"/>
       <c r="U267" s="1"/>
       <c r="V267" s="20" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="W267" s="1"/>
     </row>
@@ -10667,7 +10673,7 @@
       <c r="T268" s="1"/>
       <c r="U268" s="1"/>
       <c r="V268" s="20" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="W268" s="1"/>
     </row>
@@ -10696,7 +10702,7 @@
       <c r="T269" s="1"/>
       <c r="U269" s="1"/>
       <c r="V269" s="20" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="W269" s="1"/>
     </row>
@@ -10725,7 +10731,7 @@
       <c r="T270" s="1"/>
       <c r="U270" s="1"/>
       <c r="V270" s="20" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="W270" s="1"/>
     </row>
@@ -10754,7 +10760,7 @@
       <c r="T271" s="1"/>
       <c r="U271" s="1"/>
       <c r="V271" s="20" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="W271" s="1"/>
     </row>
@@ -10783,7 +10789,7 @@
       <c r="T272" s="1"/>
       <c r="U272" s="1"/>
       <c r="V272" s="20" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="W272" s="1"/>
     </row>
@@ -10812,7 +10818,7 @@
       <c r="T273" s="1"/>
       <c r="U273" s="1"/>
       <c r="V273" s="20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="274" spans="1:22" x14ac:dyDescent="0.4">
@@ -10840,7 +10846,7 @@
       <c r="T274" s="1"/>
       <c r="U274" s="1"/>
       <c r="V274" s="20" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="275" spans="1:22" x14ac:dyDescent="0.4">
@@ -10868,7 +10874,7 @@
       <c r="T275" s="1"/>
       <c r="U275" s="1"/>
       <c r="V275" s="20" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="276" spans="1:22" x14ac:dyDescent="0.4">
@@ -10896,7 +10902,7 @@
       <c r="T276" s="1"/>
       <c r="U276" s="1"/>
       <c r="V276" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="277" spans="1:22" x14ac:dyDescent="0.4">
@@ -10924,7 +10930,7 @@
       <c r="T277" s="1"/>
       <c r="U277" s="1"/>
       <c r="V277" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="278" spans="1:22" x14ac:dyDescent="0.4">
@@ -10952,7 +10958,7 @@
       <c r="T278" s="1"/>
       <c r="U278" s="1"/>
       <c r="V278" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="279" spans="1:22" x14ac:dyDescent="0.4">
@@ -10980,7 +10986,7 @@
       <c r="T279" s="1"/>
       <c r="U279" s="1"/>
       <c r="V279" s="20" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="280" spans="1:22" x14ac:dyDescent="0.4">
@@ -11008,7 +11014,7 @@
       <c r="T280" s="1"/>
       <c r="U280" s="1"/>
       <c r="V280" s="20" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="281" spans="1:22" x14ac:dyDescent="0.4">
@@ -11036,7 +11042,7 @@
       <c r="T281" s="1"/>
       <c r="U281" s="1"/>
       <c r="V281" s="20" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="282" spans="1:22" x14ac:dyDescent="0.4">
@@ -11064,7 +11070,7 @@
       <c r="T282" s="1"/>
       <c r="U282" s="1"/>
       <c r="V282" s="20" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="283" spans="1:22" x14ac:dyDescent="0.4">
@@ -11092,7 +11098,7 @@
       <c r="T283" s="1"/>
       <c r="U283" s="1"/>
       <c r="V283" s="20" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="284" spans="1:22" x14ac:dyDescent="0.4">
@@ -11120,7 +11126,7 @@
       <c r="T284" s="1"/>
       <c r="U284" s="1"/>
       <c r="V284" s="20" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="285" spans="1:22" x14ac:dyDescent="0.4">
@@ -11148,7 +11154,7 @@
       <c r="T285" s="1"/>
       <c r="U285" s="1"/>
       <c r="V285" s="20" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="286" spans="1:22" x14ac:dyDescent="0.4">
@@ -11176,7 +11182,7 @@
       <c r="T286" s="1"/>
       <c r="U286" s="1"/>
       <c r="V286" s="20" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="287" spans="1:22" x14ac:dyDescent="0.4">
@@ -11204,7 +11210,7 @@
       <c r="T287" s="1"/>
       <c r="U287" s="1"/>
       <c r="V287" s="20" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="288" spans="1:22" x14ac:dyDescent="0.4">
@@ -11232,7 +11238,7 @@
       <c r="T288" s="1"/>
       <c r="U288" s="1"/>
       <c r="V288" s="20" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="289" spans="1:23" s="15" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -11329,7 +11335,7 @@
       <c r="T290" s="1"/>
       <c r="U290" s="1"/>
       <c r="V290" s="20" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="W290" s="1"/>
     </row>
@@ -11358,7 +11364,7 @@
       <c r="T291" s="1"/>
       <c r="U291" s="1"/>
       <c r="V291" s="20" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="W291" s="1"/>
     </row>
@@ -11387,7 +11393,7 @@
       <c r="T292" s="1"/>
       <c r="U292" s="1"/>
       <c r="V292" s="20" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="W292" s="1"/>
     </row>
@@ -11416,7 +11422,7 @@
       <c r="T293" s="1"/>
       <c r="U293" s="1"/>
       <c r="V293" s="20" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="W293" s="1"/>
     </row>
@@ -11445,7 +11451,7 @@
       <c r="T294" s="1"/>
       <c r="U294" s="1"/>
       <c r="V294" s="20" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="W294" s="1"/>
     </row>
@@ -11474,7 +11480,7 @@
       <c r="T295" s="1"/>
       <c r="U295" s="1"/>
       <c r="V295" s="20" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="W295" s="1"/>
     </row>
@@ -11503,7 +11509,7 @@
       <c r="T296" s="1"/>
       <c r="U296" s="1"/>
       <c r="V296" s="20" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="W296" s="1"/>
     </row>
@@ -11532,7 +11538,7 @@
       <c r="T297" s="1"/>
       <c r="U297" s="1"/>
       <c r="V297" s="20" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="W297" s="1"/>
     </row>
@@ -11561,7 +11567,7 @@
       <c r="T298" s="1"/>
       <c r="U298" s="1"/>
       <c r="V298" s="20" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="W298" s="1"/>
     </row>
@@ -11590,7 +11596,7 @@
       <c r="T299" s="1"/>
       <c r="U299" s="1"/>
       <c r="V299" s="20" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="W299" s="1"/>
     </row>
@@ -11619,7 +11625,7 @@
       <c r="T300" s="1"/>
       <c r="U300" s="1"/>
       <c r="V300" s="20" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="W300" s="1"/>
     </row>
@@ -11648,7 +11654,7 @@
       <c r="T301" s="1"/>
       <c r="U301" s="1"/>
       <c r="V301" s="20" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="W301" s="1"/>
     </row>
@@ -11677,7 +11683,7 @@
       <c r="T302" s="1"/>
       <c r="U302" s="1"/>
       <c r="V302" s="20" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="W302" s="1"/>
     </row>
@@ -11706,7 +11712,7 @@
       <c r="T303" s="1"/>
       <c r="U303" s="1"/>
       <c r="V303" s="20" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="W303" s="1"/>
     </row>
@@ -11735,7 +11741,7 @@
       <c r="T304" s="1"/>
       <c r="U304" s="1"/>
       <c r="V304" s="20" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="W304" s="1"/>
     </row>
@@ -11764,7 +11770,7 @@
       <c r="T305" s="1"/>
       <c r="U305" s="1"/>
       <c r="V305" s="20" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="W305" s="1"/>
     </row>
@@ -11793,7 +11799,7 @@
       <c r="T306" s="1"/>
       <c r="U306" s="1"/>
       <c r="V306" s="20" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="W306" s="1"/>
     </row>
@@ -11822,7 +11828,7 @@
       <c r="T307" s="1"/>
       <c r="U307" s="1"/>
       <c r="V307" s="20" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="W307" s="1"/>
     </row>
@@ -11851,7 +11857,7 @@
       <c r="T308" s="1"/>
       <c r="U308" s="1"/>
       <c r="V308" s="20" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="W308" s="1"/>
     </row>
@@ -11880,7 +11886,7 @@
       <c r="T309" s="1"/>
       <c r="U309" s="1"/>
       <c r="V309" s="20" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="W309" s="1"/>
     </row>
@@ -11909,7 +11915,7 @@
       <c r="T310" s="1"/>
       <c r="U310" s="1"/>
       <c r="V310" s="20" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="W310" s="1"/>
     </row>
@@ -11938,7 +11944,7 @@
       <c r="T311" s="1"/>
       <c r="U311" s="1"/>
       <c r="V311" s="20" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="W311" s="1"/>
     </row>
@@ -11967,7 +11973,7 @@
       <c r="T312" s="1"/>
       <c r="U312" s="1"/>
       <c r="V312" s="20" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="W312" s="1"/>
     </row>
@@ -11996,7 +12002,7 @@
       <c r="T313" s="1"/>
       <c r="U313" s="1"/>
       <c r="V313" s="20" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="W313" s="1"/>
     </row>
@@ -12025,7 +12031,7 @@
       <c r="T314" s="1"/>
       <c r="U314" s="1"/>
       <c r="V314" s="20" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="W314" s="1"/>
     </row>
@@ -12054,7 +12060,7 @@
       <c r="T315" s="1"/>
       <c r="U315" s="1"/>
       <c r="V315" s="20" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="W315" s="1"/>
     </row>
@@ -12083,7 +12089,7 @@
       <c r="T316" s="1"/>
       <c r="U316" s="1"/>
       <c r="V316" s="20" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="W316" s="1"/>
     </row>
@@ -12112,7 +12118,7 @@
       <c r="T317" s="1"/>
       <c r="U317" s="1"/>
       <c r="V317" s="20" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="W317" s="1"/>
     </row>
@@ -12141,7 +12147,7 @@
       <c r="T318" s="1"/>
       <c r="U318" s="1"/>
       <c r="V318" s="20" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="W318" s="1"/>
     </row>
@@ -12170,7 +12176,7 @@
       <c r="T319" s="1"/>
       <c r="U319" s="1"/>
       <c r="V319" s="20" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="W319" s="1"/>
     </row>
@@ -12268,7 +12274,7 @@
       <c r="T321" s="1"/>
       <c r="U321" s="1"/>
       <c r="V321" s="20" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="322" spans="1:22" x14ac:dyDescent="0.4">
@@ -12296,7 +12302,7 @@
       <c r="T322" s="1"/>
       <c r="U322" s="1"/>
       <c r="V322" s="20" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="323" spans="1:22" x14ac:dyDescent="0.4">
@@ -12324,7 +12330,7 @@
       <c r="T323" s="1"/>
       <c r="U323" s="1"/>
       <c r="V323" s="20" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="324" spans="1:22" x14ac:dyDescent="0.4">
@@ -12352,7 +12358,7 @@
       <c r="T324" s="1"/>
       <c r="U324" s="1"/>
       <c r="V324" s="20" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="325" spans="1:22" x14ac:dyDescent="0.4">
@@ -12380,7 +12386,7 @@
       <c r="T325" s="1"/>
       <c r="U325" s="1"/>
       <c r="V325" s="20" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="326" spans="1:22" x14ac:dyDescent="0.4">
@@ -12408,7 +12414,7 @@
       <c r="T326" s="1"/>
       <c r="U326" s="1"/>
       <c r="V326" s="20" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="327" spans="1:22" x14ac:dyDescent="0.4">
@@ -12436,7 +12442,7 @@
       <c r="T327" s="1"/>
       <c r="U327" s="1"/>
       <c r="V327" s="20" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="328" spans="1:22" x14ac:dyDescent="0.4">
@@ -12464,7 +12470,7 @@
       <c r="T328" s="1"/>
       <c r="U328" s="1"/>
       <c r="V328" s="20" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="329" spans="1:22" x14ac:dyDescent="0.4">
@@ -12492,7 +12498,7 @@
       <c r="T329" s="1"/>
       <c r="U329" s="1"/>
       <c r="V329" s="20" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="330" spans="1:22" x14ac:dyDescent="0.4">
@@ -12520,7 +12526,7 @@
       <c r="T330" s="1"/>
       <c r="U330" s="1"/>
       <c r="V330" s="20" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="331" spans="1:22" x14ac:dyDescent="0.4">
@@ -12548,7 +12554,7 @@
       <c r="T331" s="1"/>
       <c r="U331" s="1"/>
       <c r="V331" s="20" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="332" spans="1:22" x14ac:dyDescent="0.4">
@@ -12576,7 +12582,7 @@
       <c r="T332" s="1"/>
       <c r="U332" s="1"/>
       <c r="V332" s="20" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="333" spans="1:22" x14ac:dyDescent="0.4">
@@ -12604,7 +12610,7 @@
       <c r="T333" s="1"/>
       <c r="U333" s="1"/>
       <c r="V333" s="20" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="334" spans="1:22" x14ac:dyDescent="0.4">
@@ -12632,7 +12638,7 @@
       <c r="T334" s="1"/>
       <c r="U334" s="1"/>
       <c r="V334" s="20" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="335" spans="1:22" x14ac:dyDescent="0.4">
@@ -12660,7 +12666,7 @@
       <c r="T335" s="1"/>
       <c r="U335" s="1"/>
       <c r="V335" s="20" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="336" spans="1:22" x14ac:dyDescent="0.4">
@@ -12688,7 +12694,7 @@
       <c r="T336" s="1"/>
       <c r="U336" s="1"/>
       <c r="V336" s="20" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.4">
@@ -12716,7 +12722,7 @@
       <c r="T337" s="1"/>
       <c r="U337" s="1"/>
       <c r="V337" s="20" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="W337" s="1"/>
     </row>
@@ -12745,7 +12751,7 @@
       <c r="T338" s="1"/>
       <c r="U338" s="1"/>
       <c r="V338" s="20" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="W338" s="1"/>
     </row>
@@ -12774,7 +12780,7 @@
       <c r="T339" s="1"/>
       <c r="U339" s="1"/>
       <c r="V339" s="20" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="W339" s="1"/>
     </row>
@@ -12803,7 +12809,7 @@
       <c r="T340" s="1"/>
       <c r="U340" s="1"/>
       <c r="V340" s="20" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="W340" s="1"/>
     </row>
@@ -12832,7 +12838,7 @@
       <c r="T341" s="1"/>
       <c r="U341" s="1"/>
       <c r="V341" s="20" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="W341" s="1"/>
     </row>
@@ -12861,7 +12867,7 @@
       <c r="T342" s="1"/>
       <c r="U342" s="1"/>
       <c r="V342" s="20" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="W342" s="1"/>
     </row>
@@ -12890,7 +12896,7 @@
       <c r="T343" s="1"/>
       <c r="U343" s="1"/>
       <c r="V343" s="20" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="W343" s="1"/>
     </row>
@@ -12919,7 +12925,7 @@
       <c r="T344" s="1"/>
       <c r="U344" s="1"/>
       <c r="V344" s="20" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="W344" s="1"/>
     </row>
@@ -12948,7 +12954,7 @@
       <c r="T345" s="1"/>
       <c r="U345" s="1"/>
       <c r="V345" s="20" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="W345" s="1"/>
     </row>
@@ -12977,7 +12983,7 @@
       <c r="T346" s="1"/>
       <c r="U346" s="1"/>
       <c r="V346" s="20" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="W346" s="1"/>
     </row>
@@ -13006,7 +13012,7 @@
       <c r="T347" s="1"/>
       <c r="U347" s="1"/>
       <c r="V347" s="20" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="W347" s="1"/>
     </row>
@@ -13035,7 +13041,7 @@
       <c r="T348" s="1"/>
       <c r="U348" s="1"/>
       <c r="V348" s="20" t="s">
-        <v>712</v>
+        <v>745</v>
       </c>
       <c r="W348" s="1"/>
     </row>
@@ -13064,7 +13070,7 @@
       <c r="T349" s="1"/>
       <c r="U349" s="1"/>
       <c r="V349" s="20" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="W349" s="1"/>
     </row>
@@ -13093,7 +13099,7 @@
       <c r="T350" s="1"/>
       <c r="U350" s="1"/>
       <c r="V350" s="20" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="W350" s="1"/>
     </row>
@@ -13191,7 +13197,7 @@
       <c r="T352" s="1"/>
       <c r="U352" s="1"/>
       <c r="V352" s="20" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="W352" s="1"/>
     </row>
@@ -13220,7 +13226,7 @@
       <c r="T353" s="1"/>
       <c r="U353" s="1"/>
       <c r="V353" s="20" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="354" spans="1:22" x14ac:dyDescent="0.4">
@@ -13248,7 +13254,7 @@
       <c r="T354" s="1"/>
       <c r="U354" s="1"/>
       <c r="V354" s="20" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="355" spans="1:22" x14ac:dyDescent="0.4">
@@ -13276,7 +13282,7 @@
       <c r="T355" s="1"/>
       <c r="U355" s="1"/>
       <c r="V355" s="20" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="356" spans="1:22" x14ac:dyDescent="0.4">
@@ -13304,7 +13310,7 @@
       <c r="T356" s="1"/>
       <c r="U356" s="1"/>
       <c r="V356" s="20" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="357" spans="1:22" x14ac:dyDescent="0.4">
@@ -13332,7 +13338,7 @@
       <c r="T357" s="1"/>
       <c r="U357" s="1"/>
       <c r="V357" s="20" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="358" spans="1:22" x14ac:dyDescent="0.4">
@@ -13360,7 +13366,7 @@
       <c r="T358" s="1"/>
       <c r="U358" s="1"/>
       <c r="V358" s="20" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="359" spans="1:22" x14ac:dyDescent="0.4">
@@ -13388,7 +13394,7 @@
       <c r="T359" s="1"/>
       <c r="U359" s="1"/>
       <c r="V359" s="20" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="360" spans="1:22" x14ac:dyDescent="0.4">
@@ -13416,7 +13422,7 @@
       <c r="T360" s="1"/>
       <c r="U360" s="1"/>
       <c r="V360" s="20" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="361" spans="1:22" x14ac:dyDescent="0.4">
@@ -13444,7 +13450,7 @@
       <c r="T361" s="1"/>
       <c r="U361" s="1"/>
       <c r="V361" s="20" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
     </row>
     <row r="362" spans="1:22" x14ac:dyDescent="0.4">
@@ -13472,7 +13478,7 @@
       <c r="T362" s="1"/>
       <c r="U362" s="1"/>
       <c r="V362" s="20" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="363" spans="1:22" x14ac:dyDescent="0.4">
@@ -13500,7 +13506,7 @@
       <c r="T363" s="1"/>
       <c r="U363" s="1"/>
       <c r="V363" s="20" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="364" spans="1:22" x14ac:dyDescent="0.4">
@@ -13528,7 +13534,7 @@
       <c r="T364" s="1"/>
       <c r="U364" s="1"/>
       <c r="V364" s="20" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="365" spans="1:22" x14ac:dyDescent="0.4">
@@ -13556,7 +13562,7 @@
       <c r="T365" s="1"/>
       <c r="U365" s="1"/>
       <c r="V365" s="20" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="366" spans="1:22" x14ac:dyDescent="0.4">
@@ -13584,7 +13590,7 @@
       <c r="T366" s="1"/>
       <c r="U366" s="1"/>
       <c r="V366" s="20" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
     </row>
     <row r="367" spans="1:22" x14ac:dyDescent="0.4">
@@ -13612,7 +13618,7 @@
       <c r="T367" s="1"/>
       <c r="U367" s="1"/>
       <c r="V367" s="20" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
     </row>
     <row r="368" spans="1:22" x14ac:dyDescent="0.4">
@@ -13640,7 +13646,7 @@
       <c r="T368" s="1"/>
       <c r="U368" s="1"/>
       <c r="V368" s="20" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="369" spans="1:23" x14ac:dyDescent="0.4">
@@ -13668,7 +13674,7 @@
       <c r="T369" s="1"/>
       <c r="U369" s="1"/>
       <c r="V369" s="20" t="s">
-        <v>732</v>
+        <v>746</v>
       </c>
       <c r="W369" s="1"/>
     </row>
@@ -13697,7 +13703,7 @@
       <c r="T370" s="1"/>
       <c r="U370" s="1"/>
       <c r="V370" s="20" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="W370" s="1"/>
     </row>
@@ -13726,7 +13732,7 @@
       <c r="T371" s="1"/>
       <c r="U371" s="1"/>
       <c r="V371" s="20" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="W371" s="1"/>
     </row>
@@ -13755,7 +13761,7 @@
       <c r="T372" s="1"/>
       <c r="U372" s="1"/>
       <c r="V372" s="20" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="W372" s="1"/>
     </row>
@@ -13784,7 +13790,7 @@
       <c r="T373" s="1"/>
       <c r="U373" s="1"/>
       <c r="V373" s="20" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="W373" s="1"/>
     </row>
@@ -13813,7 +13819,7 @@
       <c r="T374" s="1"/>
       <c r="U374" s="1"/>
       <c r="V374" s="20" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="W374" s="1"/>
     </row>
@@ -13842,7 +13848,7 @@
       <c r="T375" s="1"/>
       <c r="U375" s="1"/>
       <c r="V375" s="20" t="s">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="W375" s="1"/>
     </row>
@@ -13871,7 +13877,7 @@
       <c r="T376" s="1"/>
       <c r="U376" s="1"/>
       <c r="V376" s="20" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="W376" s="1"/>
     </row>
@@ -13900,7 +13906,7 @@
       <c r="T377" s="1"/>
       <c r="U377" s="1"/>
       <c r="V377" s="20" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="W377" s="1"/>
     </row>
@@ -13929,7 +13935,7 @@
       <c r="T378" s="1"/>
       <c r="U378" s="1"/>
       <c r="V378" s="20" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="W378" s="1"/>
     </row>
@@ -13958,7 +13964,7 @@
       <c r="T379" s="1"/>
       <c r="U379" s="1"/>
       <c r="V379" s="20" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="W379" s="1"/>
     </row>
@@ -13987,7 +13993,7 @@
       <c r="T380" s="1"/>
       <c r="U380" s="1"/>
       <c r="V380" s="20" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="W380" s="1"/>
     </row>
@@ -14016,7 +14022,7 @@
       <c r="T381" s="1"/>
       <c r="U381" s="1"/>
       <c r="V381" s="20" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="W381" s="1"/>
     </row>
